--- a/reports/pdf_change_20260707.xlsx
+++ b/reports/pdf_change_20260707.xlsx
@@ -575,7 +575,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,385억      당일 2026-07-07  vs  전영업일 2026-07-06      매수 2종목  /  매도 0종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,102억      당일 2026-07-07  vs  전영업일 2026-07-06      매수 2종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -671,10 +671,10 @@
         <v>27</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1075096800</v>
+        <v>1081188000</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>0.2</v>
+        <v>0.212</v>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -697,10 +697,10 @@
         <v>11</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1040255700</v>
+        <v>1046149500</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>0.193</v>
+        <v>0.205</v>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,769억      당일 2026-07-07  vs  전영업일 2026-07-06      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,517억      당일 2026-07-07  vs  전영업일 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B9" s="4" t="n"/>
@@ -740,7 +740,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,420억      당일 2026-07-07  vs  전영업일 2026-07-06      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,251억      당일 2026-07-07  vs  전영업일 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -764,7 +764,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,814억      당일 2026-07-07  vs  전영업일 2026-07-06      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,694억      당일 2026-07-07  vs  전영업일 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -788,7 +788,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 366억      당일 2026-07-07  vs  전영업일 2026-07-06      매수 6종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 356억      당일 2026-07-07  vs  전영업일 2026-07-06      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -884,10 +884,10 @@
         <v>91</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>23769200</v>
+        <v>24214190</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.065</v>
+        <v>0.068</v>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
         <v>-101</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>-54782400</v>
+        <v>-56400420</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>-0.15</v>
+        <v>-0.158</v>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         <v>10</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>41440000</v>
+        <v>39565000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.113</v>
+        <v>0.111</v>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
@@ -943,10 +943,10 @@
         <v>-31</v>
       </c>
       <c r="I22" s="17" t="n">
-        <v>-46326400</v>
+        <v>-48450520</v>
       </c>
       <c r="J22" s="18" t="n">
-        <v>-0.127</v>
+        <v>-0.136</v>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         <v>10</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>62960000</v>
+        <v>63632000</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.172</v>
+        <v>0.179</v>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
@@ -983,10 +983,10 @@
         <v>-14</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>-40992000</v>
+        <v>-41442800</v>
       </c>
       <c r="J23" s="18" t="n">
-        <v>-0.112</v>
+        <v>-0.116</v>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
@@ -1004,10 +1004,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>40464000</v>
+        <v>40344000</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.111</v>
+        <v>0.113</v>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
@@ -1023,10 +1023,10 @@
         <v>-3</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>-62400000</v>
+        <v>-66912000</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>-0.17</v>
+        <v>-0.188</v>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
@@ -1044,10 +1044,10 @@
         <v>6</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>42720000</v>
+        <v>42115200</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.117</v>
+        <v>0.118</v>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
         <v>5</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>72920000</v>
+        <v>70028000</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0.199</v>
+        <v>0.197</v>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 632억      당일 2026-07-07  vs  전영업일 2026-07-06      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 596억      당일 2026-07-07  vs  전영업일 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>

--- a/reports/pdf_change_20260707.xlsx
+++ b/reports/pdf_change_20260707.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
-    <numFmt numFmtId="165" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;;0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -158,7 +157,7 @@
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -170,7 +169,7 @@
     <xf numFmtId="164" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -627,7 +626,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>전체대비비중</t>
+          <t>보유비중(전→당)</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -652,7 +651,7 @@
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>전체대비비중</t>
+          <t>보유비중(전→당)</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr">
@@ -673,8 +672,10 @@
       <c r="C6" s="11" t="n">
         <v>1081188000</v>
       </c>
-      <c r="D6" s="12" t="n">
-        <v>0.212</v>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.22%</t>
+        </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -699,8 +700,10 @@
       <c r="C7" s="11" t="n">
         <v>1046149500</v>
       </c>
-      <c r="D7" s="12" t="n">
-        <v>0.205</v>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>2.46%→2.74%</t>
+        </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -840,7 +843,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>전체대비비중</t>
+          <t>보유비중(전→당)</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -865,7 +868,7 @@
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>전체대비비중</t>
+          <t>보유비중(전→당)</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
@@ -886,8 +889,10 @@
       <c r="C21" s="11" t="n">
         <v>24214190</v>
       </c>
-      <c r="D21" s="12" t="n">
-        <v>0.068</v>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>0.39%→0.46%</t>
+        </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
@@ -905,8 +910,10 @@
       <c r="I21" s="17" t="n">
         <v>-56400420</v>
       </c>
-      <c r="J21" s="18" t="n">
-        <v>-0.158</v>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>0.46%→0.30%</t>
+        </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
@@ -917,21 +924,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>39565000</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>0.111</v>
+        <v>63632000</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>2.62%→2.79%</t>
+        </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>186→196</t>
+          <t>142→152</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
@@ -945,8 +954,10 @@
       <c r="I22" s="17" t="n">
         <v>-48450520</v>
       </c>
-      <c r="J22" s="18" t="n">
-        <v>-0.136</v>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>0.34%→0.20%</t>
+        </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
@@ -957,21 +968,23 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>63632000</v>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>0.179</v>
+        <v>39565000</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>2.13%→2.24%</t>
+        </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>142→152</t>
+          <t>186→196</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
@@ -985,8 +998,10 @@
       <c r="I23" s="17" t="n">
         <v>-41442800</v>
       </c>
-      <c r="J23" s="18" t="n">
-        <v>-0.116</v>
+      <c r="J23" s="18" t="inlineStr">
+        <is>
+          <t>0.71%→0.59%</t>
+        </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
@@ -1006,8 +1021,10 @@
       <c r="C24" s="11" t="n">
         <v>40344000</v>
       </c>
-      <c r="D24" s="12" t="n">
-        <v>0.113</v>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>0.90%→1.01%</t>
+        </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
@@ -1025,8 +1042,10 @@
       <c r="I24" s="17" t="n">
         <v>-66912000</v>
       </c>
-      <c r="J24" s="18" t="n">
-        <v>-0.188</v>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>1.74%→1.55%</t>
+        </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
@@ -1046,8 +1065,10 @@
       <c r="C25" s="11" t="n">
         <v>42115200</v>
       </c>
-      <c r="D25" s="12" t="n">
-        <v>0.118</v>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>1.48%→1.60%</t>
+        </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
@@ -1072,8 +1093,10 @@
       <c r="C26" s="11" t="n">
         <v>70028000</v>
       </c>
-      <c r="D26" s="12" t="n">
-        <v>0.197</v>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>2.55%→2.75%</t>
+        </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>

--- a/reports/pdf_change_20260707.xlsx
+++ b/reports/pdf_change_20260707.xlsx
@@ -924,23 +924,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>63632000</v>
+        <v>39565000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2.62%→2.79%</t>
+          <t>2.13%→2.24%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>142→152</t>
+          <t>186→196</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
@@ -968,23 +968,23 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>39565000</v>
+        <v>63632000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>2.13%→2.24%</t>
+          <t>2.62%→2.79%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>186→196</t>
+          <t>142→152</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
@@ -1012,23 +1012,23 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>40344000</v>
+        <v>42115200</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>0.90%→1.01%</t>
+          <t>1.48%→1.60%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>46→52</t>
+          <t>73→79</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
@@ -1056,23 +1056,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>42115200</v>
+        <v>40344000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>1.48%→1.60%</t>
+          <t>0.90%→1.01%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>46→52</t>
         </is>
       </c>
       <c r="G25" s="14" t="n"/>

--- a/reports/pdf_change_20260707.xlsx
+++ b/reports/pdf_change_20260707.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,15 +60,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000070C0"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -93,11 +89,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4E4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E4ECF6"/>
       </patternFill>
     </fill>
     <fill>
@@ -132,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -165,17 +156,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +551,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 6/7  ·  대기: TIGER</t>
+          <t>캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
@@ -789,386 +773,80 @@
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 356억      당일 2026-07-07  vs  전영업일 2026-07-06      매수 6종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="17" t="n"/>
+      <c r="I18" s="17" t="n"/>
+      <c r="J18" s="17" t="n"/>
+      <c r="K18" s="17" t="n"/>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 596억      당일 2026-07-07  vs  전영업일 2026-07-06      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>에이프로</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>91</v>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>24214190</v>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>0.39%→0.46%</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>510→601</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>LS증권</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="n">
-        <v>-101</v>
-      </c>
-      <c r="I21" s="17" t="n">
-        <v>-56400420</v>
-      </c>
-      <c r="J21" s="18" t="inlineStr">
-        <is>
-          <t>0.46%→0.30%</t>
-        </is>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
-        <is>
-          <t>285→184</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C22" s="11" t="n">
-        <v>39565000</v>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>2.13%→2.24%</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>186→196</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>다우데이타</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="n">
-        <v>-31</v>
-      </c>
-      <c r="I22" s="17" t="n">
-        <v>-48450520</v>
-      </c>
-      <c r="J22" s="18" t="inlineStr">
-        <is>
-          <t>0.34%→0.20%</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="inlineStr">
-        <is>
-          <t>75→44</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>코미코</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C23" s="11" t="n">
-        <v>63632000</v>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>2.62%→2.79%</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>142→152</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>솔브레인홀딩스</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="n">
-        <v>-14</v>
-      </c>
-      <c r="I23" s="17" t="n">
-        <v>-41442800</v>
-      </c>
-      <c r="J23" s="18" t="inlineStr">
-        <is>
-          <t>0.71%→0.59%</t>
-        </is>
-      </c>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>83→69</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>대주전자재료</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C24" s="11" t="n">
-        <v>42115200</v>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>1.48%→1.60%</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>73→79</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>파크시스템스</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I24" s="17" t="n">
-        <v>-66912000</v>
-      </c>
-      <c r="J24" s="18" t="inlineStr">
-        <is>
-          <t>1.74%→1.55%</t>
-        </is>
-      </c>
-      <c r="K24" s="13" t="inlineStr">
-        <is>
-          <t>27→24</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>씨엠티엑스</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C25" s="11" t="n">
-        <v>40344000</v>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>0.90%→1.01%</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>46→52</t>
-        </is>
-      </c>
-      <c r="G25" s="14" t="n"/>
-      <c r="H25" s="14" t="n"/>
-      <c r="I25" s="14" t="n"/>
-      <c r="J25" s="14" t="n"/>
-      <c r="K25" s="14" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" s="11" t="n">
-        <v>70028000</v>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>2.55%→2.75%</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>63→68</t>
-        </is>
-      </c>
-      <c r="G26" s="14" t="n"/>
-      <c r="H26" s="14" t="n"/>
-      <c r="I26" s="14" t="n"/>
-      <c r="J26" s="14" t="n"/>
-      <c r="K26" s="14" t="n"/>
-    </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 596억      당일 2026-07-07  vs  전영업일 2026-07-06      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n"/>
-      <c r="C31" s="20" t="n"/>
-      <c r="D31" s="20" t="n"/>
-      <c r="E31" s="20" t="n"/>
-      <c r="F31" s="20" t="n"/>
-      <c r="G31" s="20" t="n"/>
-      <c r="H31" s="20" t="n"/>
-      <c r="I31" s="20" t="n"/>
-      <c r="J31" s="20" t="n"/>
-      <c r="K31" s="20" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="17" t="n"/>
+      <c r="H23" s="17" t="n"/>
+      <c r="I23" s="17" t="n"/>
+      <c r="J23" s="17" t="n"/>
+      <c r="K23" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="15">
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A18:K18"/>
     <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A21:K21"/>
     <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A29:K29"/>
-    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A10:K10"/>
-    <mergeCell ref="G19:K19"/>
-    <mergeCell ref="A28:K28"/>
     <mergeCell ref="A13:K13"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A9:K9"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
